--- a/output/yearly_benthic_cover_iteration_63_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_63_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.07989091789764</v>
+        <v>45.12741604471633</v>
       </c>
       <c r="M2" t="n">
-        <v>101.2143493629796</v>
+        <v>100.3702536847573</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.01962632405741</v>
+        <v>87.93032655287914</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90328996449454</v>
+        <v>45.8646250583474</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228730167359403</v>
+        <v>2.228530214495089</v>
       </c>
       <c r="E3" t="n">
-        <v>5.691506426993338</v>
+        <v>5.66453302458766</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429100557864677</v>
+        <v>0.7428434048316964</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96437298524209</v>
+        <v>33.95188615567546</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17386256617751</v>
+        <v>34.17079662225803</v>
       </c>
       <c r="I3" t="n">
-        <v>6.575056273833169</v>
+        <v>6.528965850833091</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643187848665423</v>
+        <v>4.642771280198103</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98037367594258</v>
+        <v>12.06967344712088</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8803255092544</v>
+        <v>48.83132402696618</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7639891496915</v>
+        <v>106.7656225324344</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.00639962900998</v>
+        <v>86.93959072501077</v>
       </c>
       <c r="C4" t="n">
-        <v>42.52749520058846</v>
+        <v>42.50385778433725</v>
       </c>
       <c r="D4" t="n">
-        <v>2.17939005403974</v>
+        <v>2.180314986412161</v>
       </c>
       <c r="E4" t="n">
-        <v>6.48062987090049</v>
+        <v>6.450674766462023</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444728242004162</v>
+        <v>0.7443962511698025</v>
       </c>
       <c r="G4" t="n">
-        <v>33.21246230692584</v>
+        <v>33.21732221564275</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24574991321914</v>
+        <v>34.24222755381091</v>
       </c>
       <c r="I4" t="n">
-        <v>5.490739508471742</v>
+        <v>5.452178381701859</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652955151252601</v>
+        <v>4.652476569811266</v>
       </c>
       <c r="K4" t="n">
-        <v>12.99360037099003</v>
+        <v>13.06040927498924</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29626397637058</v>
+        <v>44.25437277815038</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81735954794908</v>
+        <v>99.81863983747687</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.70226653809812</v>
+        <v>85.65892100556007</v>
       </c>
       <c r="C5" t="n">
-        <v>42.0754246746646</v>
+        <v>42.06928549769464</v>
       </c>
       <c r="D5" t="n">
-        <v>2.115276653764965</v>
+        <v>2.117335103129419</v>
       </c>
       <c r="E5" t="n">
-        <v>7.053944692602586</v>
+        <v>7.022930853249647</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458000917130911</v>
+        <v>0.7457147133241149</v>
       </c>
       <c r="G5" t="n">
-        <v>32.23541651099416</v>
+        <v>32.25781724083679</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30680421880219</v>
+        <v>34.30287681290928</v>
       </c>
       <c r="I5" t="n">
-        <v>4.583773797014297</v>
+        <v>4.55152932383511</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66125057320682</v>
+        <v>4.660716958275719</v>
       </c>
       <c r="K5" t="n">
-        <v>14.29773346190188</v>
+        <v>14.34107899443992</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47432132153153</v>
+        <v>43.43818610837372</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84747945809801</v>
+        <v>99.84855060050829</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.32142443868182</v>
+        <v>84.15981537526817</v>
       </c>
       <c r="C6" t="n">
-        <v>41.40623109924383</v>
+        <v>41.2768491307807</v>
       </c>
       <c r="D6" t="n">
-        <v>2.047824565173154</v>
+        <v>2.043732507019083</v>
       </c>
       <c r="E6" t="n">
-        <v>7.466606050646144</v>
+        <v>7.411908370839289</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469279679948123</v>
+        <v>0.7468366690091124</v>
       </c>
       <c r="G6" t="n">
-        <v>31.20749131434275</v>
+        <v>31.13647414768674</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35868652776136</v>
+        <v>34.35448677441916</v>
       </c>
       <c r="I6" t="n">
-        <v>3.825588212796024</v>
+        <v>3.798647724987819</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668299799967577</v>
+        <v>4.667729181306953</v>
       </c>
       <c r="K6" t="n">
-        <v>15.67857556131817</v>
+        <v>15.84018462473185</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78786628952093</v>
+        <v>42.75653487438093</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87267295008293</v>
+        <v>99.87356862989347</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.82301133043258</v>
+        <v>82.49802241221444</v>
       </c>
       <c r="C7" t="n">
-        <v>40.50176848612929</v>
+        <v>40.20474869330437</v>
       </c>
       <c r="D7" t="n">
-        <v>1.975006384847311</v>
+        <v>1.962574731235275</v>
       </c>
       <c r="E7" t="n">
-        <v>7.733116812280276</v>
+        <v>7.645842922920191</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478875475919843</v>
+        <v>0.7477931238042436</v>
       </c>
       <c r="G7" t="n">
-        <v>30.09779043044265</v>
+        <v>29.90002711809868</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40282718923127</v>
+        <v>34.3984836949952</v>
       </c>
       <c r="I7" t="n">
-        <v>3.192085793589193</v>
+        <v>3.169593797384304</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674297172449902</v>
+        <v>4.673707023776523</v>
       </c>
       <c r="K7" t="n">
-        <v>17.17698866956741</v>
+        <v>17.50197758778557</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21497650505896</v>
+        <v>42.1877557265493</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89373366075566</v>
+        <v>99.89448200763923</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.72704258731669</v>
+        <v>87.47959914656835</v>
       </c>
       <c r="C8" t="n">
-        <v>42.7460479318044</v>
+        <v>42.5187989207263</v>
       </c>
       <c r="D8" t="n">
-        <v>1.979303272191884</v>
+        <v>1.966845583438594</v>
       </c>
       <c r="E8" t="n">
-        <v>9.532721703045819</v>
+        <v>9.491418725869043</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495146757689191</v>
+        <v>0.7494204319824221</v>
       </c>
       <c r="G8" t="n">
-        <v>30.57750795603824</v>
+        <v>30.40364135975856</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47767508537027</v>
+        <v>34.47333987119141</v>
       </c>
       <c r="I8" t="n">
-        <v>5.725853171345802</v>
+        <v>5.711055474438176</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684466723555744</v>
+        <v>4.683877699890139</v>
       </c>
       <c r="K8" t="n">
-        <v>12.27295741268331</v>
+        <v>12.52040085343166</v>
       </c>
       <c r="L8" t="n">
-        <v>44.79054722667904</v>
+        <v>44.77084508045267</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80955257116675</v>
+        <v>99.81004485461062</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.79789789766856</v>
+        <v>85.44110784018571</v>
       </c>
       <c r="C9" t="n">
-        <v>41.70516030230589</v>
+        <v>41.36603694389352</v>
       </c>
       <c r="D9" t="n">
-        <v>1.892090816187745</v>
+        <v>1.87454934309794</v>
       </c>
       <c r="E9" t="n">
-        <v>9.909423380773049</v>
+        <v>9.840701841147206</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7509067007807343</v>
+        <v>0.7508144861541038</v>
       </c>
       <c r="G9" t="n">
-        <v>29.23019569480046</v>
+        <v>28.97691939754665</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54170823591377</v>
+        <v>34.53746636308877</v>
       </c>
       <c r="I9" t="n">
-        <v>4.780406189333214</v>
+        <v>4.768065870687896</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693166879879589</v>
+        <v>4.69259053846315</v>
       </c>
       <c r="K9" t="n">
-        <v>14.20210210233142</v>
+        <v>14.55889215981428</v>
       </c>
       <c r="L9" t="n">
-        <v>43.93368611838085</v>
+        <v>43.9164304664467</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84094852301817</v>
+        <v>99.84135957015451</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.68730210534108</v>
+        <v>83.31112213990576</v>
       </c>
       <c r="C10" t="n">
-        <v>40.33596610428854</v>
+        <v>39.97523073859482</v>
       </c>
       <c r="D10" t="n">
-        <v>1.797617471471486</v>
+        <v>1.779256800494445</v>
       </c>
       <c r="E10" t="n">
-        <v>10.07963980293262</v>
+        <v>10.00373652142335</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7521000797129183</v>
+        <v>0.7520100159008908</v>
       </c>
       <c r="G10" t="n">
-        <v>27.77071270890313</v>
+        <v>27.50388037812806</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59660366679424</v>
+        <v>34.59246073144097</v>
       </c>
       <c r="I10" t="n">
-        <v>3.990002877320932</v>
+        <v>3.979715093137481</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700625498205739</v>
+        <v>4.700062599380568</v>
       </c>
       <c r="K10" t="n">
-        <v>16.31269789465892</v>
+        <v>16.68887786009424</v>
       </c>
       <c r="L10" t="n">
-        <v>43.21854694023771</v>
+        <v>43.20344512712516</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86721093918518</v>
+        <v>99.86755372581422</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.47167884507955</v>
+        <v>81.04629569778412</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73861386905318</v>
+        <v>38.32679548120529</v>
       </c>
       <c r="D11" t="n">
-        <v>1.699474264678654</v>
+        <v>1.678975578931094</v>
       </c>
       <c r="E11" t="n">
-        <v>10.08425105583403</v>
+        <v>9.99340612835068</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753124624363413</v>
+        <v>0.7530371631827861</v>
       </c>
       <c r="G11" t="n">
-        <v>26.25453541121412</v>
+        <v>25.9537259983418</v>
       </c>
       <c r="H11" t="n">
-        <v>34.643732720717</v>
+        <v>34.63970950640815</v>
       </c>
       <c r="I11" t="n">
-        <v>3.329531866001</v>
+        <v>3.320959052677178</v>
       </c>
       <c r="J11" t="n">
-        <v>4.707028902271332</v>
+        <v>4.706482269892414</v>
       </c>
       <c r="K11" t="n">
-        <v>18.52832115492047</v>
+        <v>18.95370430221589</v>
       </c>
       <c r="L11" t="n">
-        <v>42.62223156276742</v>
+        <v>42.60895257510277</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88916658674107</v>
+        <v>99.88945235852395</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.05257221882452</v>
+        <v>78.77044661936276</v>
       </c>
       <c r="C12" t="n">
-        <v>36.83471371122424</v>
+        <v>36.56454010325683</v>
       </c>
       <c r="D12" t="n">
-        <v>1.593257384844184</v>
+        <v>1.579270725766351</v>
       </c>
       <c r="E12" t="n">
-        <v>9.916963555376332</v>
+        <v>9.861739435762823</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7540067692361534</v>
+        <v>0.7539200865816492</v>
       </c>
       <c r="G12" t="n">
-        <v>24.61363099104035</v>
+        <v>24.41248116297016</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68431138486306</v>
+        <v>34.68032398275586</v>
       </c>
       <c r="I12" t="n">
-        <v>2.777859825738507</v>
+        <v>2.770710684390612</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712542307725959</v>
+        <v>4.712000541135309</v>
       </c>
       <c r="K12" t="n">
-        <v>20.94742778117547</v>
+        <v>21.22955338063725</v>
       </c>
       <c r="L12" t="n">
-        <v>42.1253715113225</v>
+        <v>42.11365765353155</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90751300372222</v>
+        <v>99.90775113742563</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.73884770381162</v>
+        <v>76.43234693047805</v>
       </c>
       <c r="C13" t="n">
-        <v>34.94994805017001</v>
+        <v>34.65413265058387</v>
       </c>
       <c r="D13" t="n">
-        <v>1.492710567748353</v>
+        <v>1.477770415573939</v>
       </c>
       <c r="E13" t="n">
-        <v>9.677328944796526</v>
+        <v>9.613130633981136</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547657044614894</v>
+        <v>0.7546800178850335</v>
       </c>
       <c r="G13" t="n">
-        <v>23.06032122649001</v>
+        <v>22.84348202293641</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71922240522851</v>
+        <v>34.71528082271153</v>
       </c>
       <c r="I13" t="n">
-        <v>2.317213202202403</v>
+        <v>2.311252905608524</v>
       </c>
       <c r="J13" t="n">
-        <v>4.717285652884309</v>
+        <v>4.716750111781461</v>
       </c>
       <c r="K13" t="n">
-        <v>23.26115229618838</v>
+        <v>23.56765306952195</v>
       </c>
       <c r="L13" t="n">
-        <v>41.71173688070444</v>
+        <v>41.70125009421668</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92283722706284</v>
+        <v>99.9230358143225</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.44631998970466</v>
+        <v>83.33172058018793</v>
       </c>
       <c r="C14" t="n">
-        <v>39.07172476977229</v>
+        <v>38.88635498901078</v>
       </c>
       <c r="D14" t="n">
-        <v>1.494529720931011</v>
+        <v>1.479586254230367</v>
       </c>
       <c r="E14" t="n">
-        <v>11.98915016643756</v>
+        <v>11.9821562656122</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556855307580923</v>
+        <v>0.755607345388188</v>
       </c>
       <c r="G14" t="n">
-        <v>24.87997571747204</v>
+        <v>24.71678747606727</v>
       </c>
       <c r="H14" t="n">
-        <v>36.55308549608505</v>
+        <v>36.60317397563309</v>
       </c>
       <c r="I14" t="n">
-        <v>3.050858790782838</v>
+        <v>3.071863354580625</v>
       </c>
       <c r="J14" t="n">
-        <v>4.723034567238077</v>
+        <v>4.722545908676176</v>
       </c>
       <c r="K14" t="n">
-        <v>16.55368001029534</v>
+        <v>16.66827941981207</v>
       </c>
       <c r="L14" t="n">
-        <v>44.27302371120669</v>
+        <v>44.34309581197127</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89842849127432</v>
+        <v>99.89773022079412</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.73180401055383</v>
+        <v>82.67779806934321</v>
       </c>
       <c r="C15" t="n">
-        <v>38.8285555440566</v>
+        <v>38.70561897149747</v>
       </c>
       <c r="D15" t="n">
-        <v>1.468198326316992</v>
+        <v>1.455601584276407</v>
       </c>
       <c r="E15" t="n">
-        <v>12.20208402156572</v>
+        <v>12.21625414820209</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564604087292304</v>
+        <v>0.7563879931464634</v>
       </c>
       <c r="G15" t="n">
-        <v>24.44162748696922</v>
+        <v>24.31736354782216</v>
       </c>
       <c r="H15" t="n">
-        <v>36.5905669345607</v>
+        <v>36.64223499056276</v>
       </c>
       <c r="I15" t="n">
-        <v>2.544989277854272</v>
+        <v>2.562530848167917</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72787755455769</v>
+        <v>4.727424957165398</v>
       </c>
       <c r="K15" t="n">
-        <v>17.26819598944617</v>
+        <v>17.32220193065679</v>
       </c>
       <c r="L15" t="n">
-        <v>43.81850238897549</v>
+        <v>43.8868495602185</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91525392247826</v>
+        <v>99.91467046237277</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.35663233723841</v>
+        <v>80.33960883204675</v>
       </c>
       <c r="C16" t="n">
-        <v>36.84666930330105</v>
+        <v>36.76332509839622</v>
       </c>
       <c r="D16" t="n">
-        <v>1.377910987867525</v>
+        <v>1.36722248360131</v>
       </c>
       <c r="E16" t="n">
-        <v>11.8054948301831</v>
+        <v>11.83074806804954</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571264945251038</v>
+        <v>0.7570587520916995</v>
       </c>
       <c r="G16" t="n">
-        <v>22.9385815744272</v>
+        <v>22.84089722327205</v>
       </c>
       <c r="H16" t="n">
-        <v>36.62278601254128</v>
+        <v>36.67472903742239</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1226918469123</v>
+        <v>2.137336067036649</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732040590781899</v>
+        <v>4.731617200573123</v>
       </c>
       <c r="K16" t="n">
-        <v>19.6433676627616</v>
+        <v>19.66039116795324</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43926888733029</v>
+        <v>43.50510232120143</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92930585339293</v>
+        <v>99.92881858755089</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.07106817064164</v>
+        <v>82.17583046816181</v>
       </c>
       <c r="C17" t="n">
-        <v>38.0919939297464</v>
+        <v>38.0857925631159</v>
       </c>
       <c r="D17" t="n">
-        <v>1.379100696982647</v>
+        <v>1.368413709896116</v>
       </c>
       <c r="E17" t="n">
-        <v>12.59980499631363</v>
+        <v>12.66554512622315</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757780208952065</v>
+        <v>0.7577183581931363</v>
       </c>
       <c r="G17" t="n">
-        <v>23.38819722918847</v>
+        <v>23.3272985544985</v>
       </c>
       <c r="H17" t="n">
-        <v>37.08421681566595</v>
+        <v>37.17318343566068</v>
       </c>
       <c r="I17" t="n">
-        <v>2.125841917588459</v>
+        <v>2.147931544983126</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736126305950406</v>
+        <v>4.735739738707102</v>
       </c>
       <c r="K17" t="n">
-        <v>17.92893182935835</v>
+        <v>17.82416953183818</v>
       </c>
       <c r="L17" t="n">
-        <v>43.90827397366014</v>
+        <v>44.01850251385295</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92919973276491</v>
+        <v>99.92846460880703</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.83576609275023</v>
+        <v>79.90038472664378</v>
       </c>
       <c r="C18" t="n">
-        <v>36.18483687543271</v>
+        <v>36.14185383298496</v>
       </c>
       <c r="D18" t="n">
-        <v>1.29756257273279</v>
+        <v>1.286032329025279</v>
       </c>
       <c r="E18" t="n">
-        <v>12.15032690201911</v>
+        <v>12.20159945702743</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583411220420687</v>
+        <v>0.7582845991777424</v>
       </c>
       <c r="G18" t="n">
-        <v>22.00539049446188</v>
+        <v>21.92294616237597</v>
       </c>
       <c r="H18" t="n">
-        <v>37.11166675748115</v>
+        <v>37.20096286024761</v>
       </c>
       <c r="I18" t="n">
-        <v>1.772846231250316</v>
+        <v>1.791280573928857</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73963201276293</v>
+        <v>4.739278744860891</v>
       </c>
       <c r="K18" t="n">
-        <v>20.16423390724975</v>
+        <v>20.09961527335622</v>
       </c>
       <c r="L18" t="n">
-        <v>43.59187805294007</v>
+        <v>43.69886612852039</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94094883562252</v>
+        <v>99.94033523486158</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.94945408283326</v>
+        <v>79.0387636714886</v>
       </c>
       <c r="C19" t="n">
-        <v>35.57153772456809</v>
+        <v>35.55603046105248</v>
       </c>
       <c r="D19" t="n">
-        <v>1.265913869925517</v>
+        <v>1.255530597980917</v>
       </c>
       <c r="E19" t="n">
-        <v>12.10035197214132</v>
+        <v>12.16115125092682</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588144422258307</v>
+        <v>0.7587622677880488</v>
       </c>
       <c r="G19" t="n">
-        <v>21.4686594893047</v>
+        <v>21.40298426682111</v>
       </c>
       <c r="H19" t="n">
-        <v>37.13483008123981</v>
+        <v>37.22439698016878</v>
       </c>
       <c r="I19" t="n">
-        <v>1.478293964084661</v>
+        <v>1.493674134127607</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742590263911443</v>
+        <v>4.742264173675306</v>
       </c>
       <c r="K19" t="n">
-        <v>21.05054591716673</v>
+        <v>20.9612363285114</v>
       </c>
       <c r="L19" t="n">
-        <v>43.32867062961934</v>
+        <v>43.43297541671588</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95075427135416</v>
+        <v>99.95024220627977</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.57784615368425</v>
+        <v>76.64648995316519</v>
       </c>
       <c r="C20" t="n">
-        <v>33.42745045057121</v>
+        <v>33.39360940604454</v>
       </c>
       <c r="D20" t="n">
-        <v>1.180361725546908</v>
+        <v>1.16990308299598</v>
       </c>
       <c r="E20" t="n">
-        <v>11.48802284338662</v>
+        <v>11.53932465951169</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592215633998132</v>
+        <v>0.7591732300794817</v>
       </c>
       <c r="G20" t="n">
-        <v>20.01777890423594</v>
+        <v>19.9432951449655</v>
       </c>
       <c r="H20" t="n">
-        <v>37.15475376057038</v>
+        <v>37.24455853027429</v>
       </c>
       <c r="I20" t="n">
-        <v>1.232572585295761</v>
+        <v>1.245402617341477</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745134771248833</v>
+        <v>4.744832687996761</v>
       </c>
       <c r="K20" t="n">
-        <v>23.42215384631575</v>
+        <v>23.35351004683481</v>
       </c>
       <c r="L20" t="n">
-        <v>43.10933198188847</v>
+        <v>43.21138959895043</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95893627877543</v>
+        <v>99.95850905182978</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.26046693774492</v>
+        <v>82.54560574096638</v>
       </c>
       <c r="C21" t="n">
-        <v>36.91620298203527</v>
+        <v>36.99915394832606</v>
       </c>
       <c r="D21" t="n">
-        <v>1.181222777427477</v>
+        <v>1.170780630660941</v>
       </c>
       <c r="E21" t="n">
-        <v>13.38309675707537</v>
+        <v>13.4978489769797</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597754013808193</v>
+        <v>0.7597426881012961</v>
       </c>
       <c r="G21" t="n">
-        <v>21.61903772822548</v>
+        <v>21.59853482429964</v>
       </c>
       <c r="H21" t="n">
-        <v>38.76851368833848</v>
+        <v>38.91277593699914</v>
       </c>
       <c r="I21" t="n">
-        <v>1.800224326667195</v>
+        <v>1.857530883292554</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748596258630122</v>
+        <v>4.748391800633102</v>
       </c>
       <c r="K21" t="n">
-        <v>17.73953306225506</v>
+        <v>17.45439425903362</v>
       </c>
       <c r="L21" t="n">
-        <v>45.28430022058134</v>
+        <v>45.48458050636022</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94003626487167</v>
+        <v>99.93812871371991</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_63_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_63_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.12741604471633</v>
+        <v>45.49730653489574</v>
       </c>
       <c r="M2" t="n">
-        <v>100.3702536847573</v>
+        <v>98.27141251401321</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.93032655287914</v>
+        <v>88.10746329115638</v>
       </c>
       <c r="C3" t="n">
-        <v>45.8646250583474</v>
+        <v>45.96918684753438</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228530214495089</v>
+        <v>2.228905365673211</v>
       </c>
       <c r="E3" t="n">
-        <v>5.66453302458766</v>
+        <v>5.733848735172391</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428434048316964</v>
+        <v>0.7429684552244036</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95188615567546</v>
+        <v>33.98634711897323</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17079662225803</v>
+        <v>34.17654894032256</v>
       </c>
       <c r="I3" t="n">
-        <v>6.528965850833091</v>
+        <v>6.595291830638066</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642771280198103</v>
+        <v>4.643552845152522</v>
       </c>
       <c r="K3" t="n">
-        <v>12.06967344712088</v>
+        <v>11.89253670884362</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83132402696618</v>
+        <v>48.90155784866645</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7656225324344</v>
+        <v>106.7632814050445</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.93959072501077</v>
+        <v>87.13225206824448</v>
       </c>
       <c r="C4" t="n">
-        <v>42.50385778433725</v>
+        <v>42.63287120638661</v>
       </c>
       <c r="D4" t="n">
-        <v>2.180314986412161</v>
+        <v>2.181676064127546</v>
       </c>
       <c r="E4" t="n">
-        <v>6.450674766462023</v>
+        <v>6.530294378226596</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443962511698025</v>
+        <v>0.7445338974800059</v>
       </c>
       <c r="G4" t="n">
-        <v>33.21732221564275</v>
+        <v>33.26619476919736</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24222755381091</v>
+        <v>34.24855928408027</v>
       </c>
       <c r="I4" t="n">
-        <v>5.452178381701859</v>
+        <v>5.507656815882666</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652476569811266</v>
+        <v>4.653336859250036</v>
       </c>
       <c r="K4" t="n">
-        <v>13.06040927498924</v>
+        <v>12.86774793175553</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25437277815038</v>
+        <v>44.3161783110068</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81863983747687</v>
+        <v>99.81679744914894</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.65892100556007</v>
+        <v>86.02818229230078</v>
       </c>
       <c r="C5" t="n">
-        <v>42.06928549769464</v>
+        <v>42.38358166862708</v>
       </c>
       <c r="D5" t="n">
-        <v>2.117335103129419</v>
+        <v>2.128080222382072</v>
       </c>
       <c r="E5" t="n">
-        <v>7.022930853249647</v>
+        <v>7.136183941276451</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457147133241149</v>
+        <v>0.7458603176757821</v>
       </c>
       <c r="G5" t="n">
-        <v>32.25781724083679</v>
+        <v>32.44896541987276</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30287681290928</v>
+        <v>34.30957461308597</v>
       </c>
       <c r="I5" t="n">
-        <v>4.55152932383511</v>
+        <v>4.597890792534119</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660716958275719</v>
+        <v>4.661626985473638</v>
       </c>
       <c r="K5" t="n">
-        <v>14.34107899443992</v>
+        <v>13.97181770769922</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43818610837372</v>
+        <v>43.49161015656586</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84855060050829</v>
+        <v>99.84700953289214</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.15981537526817</v>
+        <v>84.81466970465333</v>
       </c>
       <c r="C6" t="n">
-        <v>41.2768491307807</v>
+        <v>41.88417325696712</v>
       </c>
       <c r="D6" t="n">
-        <v>2.043732507019083</v>
+        <v>2.069286615851562</v>
       </c>
       <c r="E6" t="n">
-        <v>7.411908370839289</v>
+        <v>7.578587815132032</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468366690091124</v>
+        <v>0.7469851742689512</v>
       </c>
       <c r="G6" t="n">
-        <v>31.13647414768674</v>
+        <v>31.55248055752925</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35448677441916</v>
+        <v>34.36131801637175</v>
       </c>
       <c r="I6" t="n">
-        <v>3.798647724987819</v>
+        <v>3.837354186318828</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667729181306953</v>
+        <v>4.668657339180944</v>
       </c>
       <c r="K6" t="n">
-        <v>15.84018462473185</v>
+        <v>15.18533029534668</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75653487438093</v>
+        <v>42.80277725900471</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87356862989347</v>
+        <v>99.87228081131852</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.49802241221444</v>
+        <v>83.3796056150528</v>
       </c>
       <c r="C7" t="n">
-        <v>40.20474869330437</v>
+        <v>41.0452419323922</v>
       </c>
       <c r="D7" t="n">
-        <v>1.962574731235275</v>
+        <v>1.999767082861641</v>
       </c>
       <c r="E7" t="n">
-        <v>7.645842922920191</v>
+        <v>7.857626464491908</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477931238042436</v>
+        <v>0.7479413486249437</v>
       </c>
       <c r="G7" t="n">
-        <v>29.90002711809868</v>
+        <v>30.49244677766047</v>
       </c>
       <c r="H7" t="n">
-        <v>34.3984836949952</v>
+        <v>34.4053020367474</v>
       </c>
       <c r="I7" t="n">
-        <v>3.169593797384304</v>
+        <v>3.201888475760537</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673707023776523</v>
+        <v>4.674633428905897</v>
       </c>
       <c r="K7" t="n">
-        <v>17.50197758778557</v>
+        <v>16.62039438494722</v>
       </c>
       <c r="L7" t="n">
-        <v>42.1877557265493</v>
+        <v>42.22777051081838</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89448200763923</v>
+        <v>99.89340682815779</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.47959914656835</v>
+        <v>88.18537967157906</v>
       </c>
       <c r="C8" t="n">
-        <v>42.5187989207263</v>
+        <v>43.36058359999819</v>
       </c>
       <c r="D8" t="n">
-        <v>1.966845583438594</v>
+        <v>2.003978364054869</v>
       </c>
       <c r="E8" t="n">
-        <v>9.491418725869043</v>
+        <v>9.695399052763799</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494204319824221</v>
+        <v>0.7495164277239531</v>
       </c>
       <c r="G8" t="n">
-        <v>30.40364135975856</v>
+        <v>31.00300219469264</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47333987119141</v>
+        <v>34.47775567530184</v>
       </c>
       <c r="I8" t="n">
-        <v>5.711055474438176</v>
+        <v>5.57125028376726</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683877699890139</v>
+        <v>4.684477673274706</v>
       </c>
       <c r="K8" t="n">
-        <v>12.52040085343166</v>
+        <v>11.81462032842093</v>
       </c>
       <c r="L8" t="n">
-        <v>44.77084508045267</v>
+        <v>44.63947798751872</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81004485461062</v>
+        <v>99.81468191593784</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.44110784018571</v>
+        <v>86.11800316046502</v>
       </c>
       <c r="C9" t="n">
-        <v>41.36603694389352</v>
+        <v>42.15830428975556</v>
       </c>
       <c r="D9" t="n">
-        <v>1.87454934309794</v>
+        <v>1.91039156764274</v>
       </c>
       <c r="E9" t="n">
-        <v>9.840701841147206</v>
+        <v>10.01779682819172</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508144861541038</v>
+        <v>0.7508657587833297</v>
       </c>
       <c r="G9" t="n">
-        <v>28.97691939754665</v>
+        <v>29.55514641610597</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53746636308877</v>
+        <v>34.53982490403316</v>
       </c>
       <c r="I9" t="n">
-        <v>4.768065870687896</v>
+        <v>4.65106669331229</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69259053846315</v>
+        <v>4.69291099239581</v>
       </c>
       <c r="K9" t="n">
-        <v>14.55889215981428</v>
+        <v>13.88199683953498</v>
       </c>
       <c r="L9" t="n">
-        <v>43.9164304664467</v>
+        <v>43.80494191838259</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84135957015451</v>
+        <v>99.84524304767312</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.31112213990576</v>
+        <v>83.73406940176716</v>
       </c>
       <c r="C10" t="n">
-        <v>39.97523073859482</v>
+        <v>40.49624829720818</v>
       </c>
       <c r="D10" t="n">
-        <v>1.779256800494445</v>
+        <v>1.803389104520092</v>
       </c>
       <c r="E10" t="n">
-        <v>10.00373652142335</v>
+        <v>10.103672255109</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520100159008908</v>
+        <v>0.7520260867881906</v>
       </c>
       <c r="G10" t="n">
-        <v>27.50388037812806</v>
+        <v>27.89974052024764</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59246073144097</v>
+        <v>34.59319999225676</v>
       </c>
       <c r="I10" t="n">
-        <v>3.979715093137481</v>
+        <v>3.881878400419283</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700062599380568</v>
+        <v>4.700163042426191</v>
       </c>
       <c r="K10" t="n">
-        <v>16.68887786009424</v>
+        <v>16.26593059823283</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20344512712516</v>
+        <v>43.10862480752255</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86755372581422</v>
+        <v>99.87080370296356</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.04629569778412</v>
+        <v>81.23080923475851</v>
       </c>
       <c r="C11" t="n">
-        <v>38.32679548120529</v>
+        <v>38.59471757749228</v>
       </c>
       <c r="D11" t="n">
-        <v>1.678975578931094</v>
+        <v>1.692228905149244</v>
       </c>
       <c r="E11" t="n">
-        <v>9.99340612835068</v>
+        <v>10.020752271621</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530371631827861</v>
+        <v>0.7530256918352967</v>
       </c>
       <c r="G11" t="n">
-        <v>25.9537259983418</v>
+        <v>26.18001142193362</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63970950640815</v>
+        <v>34.63918182442364</v>
       </c>
       <c r="I11" t="n">
-        <v>3.320959052677178</v>
+        <v>3.239198545825109</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706482269892414</v>
+        <v>4.706410573970604</v>
       </c>
       <c r="K11" t="n">
-        <v>18.95370430221589</v>
+        <v>18.76919076524149</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60895257510277</v>
+        <v>42.52826170169902</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88945235852395</v>
+        <v>99.89217004443279</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.77044661936276</v>
+        <v>78.7562872785368</v>
       </c>
       <c r="C12" t="n">
-        <v>36.56454010325683</v>
+        <v>36.62138502123759</v>
       </c>
       <c r="D12" t="n">
-        <v>1.579270725766351</v>
+        <v>1.583530622995482</v>
       </c>
       <c r="E12" t="n">
-        <v>9.861739435762823</v>
+        <v>9.827484603962036</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539200865816492</v>
+        <v>0.7538869950836452</v>
       </c>
       <c r="G12" t="n">
-        <v>24.41248116297016</v>
+        <v>24.49836997279463</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68032398275586</v>
+        <v>34.67880177384768</v>
       </c>
       <c r="I12" t="n">
-        <v>2.770710684390612</v>
+        <v>2.70241959058054</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712000541135309</v>
+        <v>4.711793719272783</v>
       </c>
       <c r="K12" t="n">
-        <v>21.22955338063725</v>
+        <v>21.24371272146321</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11365765353155</v>
+        <v>42.04492451991517</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90775113742563</v>
+        <v>99.91002226261597</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.43234693047805</v>
+        <v>76.28235821191839</v>
       </c>
       <c r="C13" t="n">
-        <v>34.65413265058387</v>
+        <v>34.56467918246471</v>
       </c>
       <c r="D13" t="n">
-        <v>1.477770415573939</v>
+        <v>1.47588777608043</v>
       </c>
       <c r="E13" t="n">
-        <v>9.613130633981136</v>
+        <v>9.535152511467023</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546800178850335</v>
+        <v>0.7546296037405491</v>
       </c>
       <c r="G13" t="n">
-        <v>22.84348202293641</v>
+        <v>22.83305687410544</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71528082271153</v>
+        <v>34.71296177206526</v>
       </c>
       <c r="I13" t="n">
-        <v>2.311252905608524</v>
+        <v>2.254234651081253</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716750111781461</v>
+        <v>4.716435023378432</v>
       </c>
       <c r="K13" t="n">
-        <v>23.56765306952195</v>
+        <v>23.71764178808159</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70125009421668</v>
+        <v>41.64261181860425</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9230358143225</v>
+        <v>99.92493278915056</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.33172058018793</v>
+        <v>83.47248356602283</v>
       </c>
       <c r="C14" t="n">
-        <v>38.88635498901078</v>
+        <v>38.80627723503814</v>
       </c>
       <c r="D14" t="n">
-        <v>1.479586254230367</v>
+        <v>1.477834043986564</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9821562656122</v>
+        <v>11.92946610429226</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755607345388188</v>
+        <v>0.7556247413130541</v>
       </c>
       <c r="G14" t="n">
-        <v>24.71678747606727</v>
+        <v>24.69452656964077</v>
       </c>
       <c r="H14" t="n">
-        <v>36.60317397563309</v>
+        <v>36.59009761648097</v>
       </c>
       <c r="I14" t="n">
-        <v>3.071863354580625</v>
+        <v>3.30227985710262</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722545908676176</v>
+        <v>4.722654633206589</v>
       </c>
       <c r="K14" t="n">
-        <v>16.66827941981207</v>
+        <v>16.52751643397716</v>
       </c>
       <c r="L14" t="n">
-        <v>44.34309581197127</v>
+        <v>44.5562753028893</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89773022079412</v>
+        <v>99.89006897190461</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.67779806934321</v>
+        <v>82.58961749054775</v>
       </c>
       <c r="C15" t="n">
-        <v>38.70561897149747</v>
+        <v>38.43323536391071</v>
       </c>
       <c r="D15" t="n">
-        <v>1.455601584276407</v>
+        <v>1.445195954943731</v>
       </c>
       <c r="E15" t="n">
-        <v>12.21625414820209</v>
+        <v>12.12516279932763</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563879931464634</v>
+        <v>0.7564649259120343</v>
       </c>
       <c r="G15" t="n">
-        <v>24.31736354782216</v>
+        <v>24.14914587528598</v>
       </c>
       <c r="H15" t="n">
-        <v>36.64223499056276</v>
+        <v>36.63078240988666</v>
       </c>
       <c r="I15" t="n">
-        <v>2.562530848167917</v>
+        <v>2.754959738241501</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727424957165398</v>
+        <v>4.727905786950215</v>
       </c>
       <c r="K15" t="n">
-        <v>17.32220193065679</v>
+        <v>17.41038250945223</v>
       </c>
       <c r="L15" t="n">
-        <v>43.8868495602185</v>
+        <v>44.06465213060641</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91467046237277</v>
+        <v>99.90827000396936</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.33960883204675</v>
+        <v>79.97468339290117</v>
       </c>
       <c r="C16" t="n">
-        <v>36.76332509839622</v>
+        <v>36.24366875480077</v>
       </c>
       <c r="D16" t="n">
-        <v>1.36722248360131</v>
+        <v>1.346294868212239</v>
       </c>
       <c r="E16" t="n">
-        <v>11.83074806804954</v>
+        <v>11.67838460522143</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570587520916995</v>
+        <v>0.7571894699578133</v>
       </c>
       <c r="G16" t="n">
-        <v>22.84089722327205</v>
+        <v>22.49651409027928</v>
       </c>
       <c r="H16" t="n">
-        <v>36.67472903742239</v>
+        <v>36.66586746720814</v>
       </c>
       <c r="I16" t="n">
-        <v>2.137336067036649</v>
+        <v>2.29799870478592</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731617200573123</v>
+        <v>4.732434187236334</v>
       </c>
       <c r="K16" t="n">
-        <v>19.66039116795324</v>
+        <v>20.02531660709882</v>
       </c>
       <c r="L16" t="n">
-        <v>43.50510232120143</v>
+        <v>43.6544879787048</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92881858755089</v>
+        <v>99.9234733406044</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.17583046816181</v>
+        <v>81.64493076213625</v>
       </c>
       <c r="C17" t="n">
-        <v>38.0857925631159</v>
+        <v>37.43301654405293</v>
       </c>
       <c r="D17" t="n">
-        <v>1.368413709896116</v>
+        <v>1.347589996959547</v>
       </c>
       <c r="E17" t="n">
-        <v>12.66554512622315</v>
+        <v>12.46384629212229</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577183581931363</v>
+        <v>0.757917882338233</v>
       </c>
       <c r="G17" t="n">
-        <v>23.3272985544985</v>
+        <v>22.89967274225495</v>
       </c>
       <c r="H17" t="n">
-        <v>37.17318343566068</v>
+        <v>37.08265696434449</v>
       </c>
       <c r="I17" t="n">
-        <v>2.147931544983126</v>
+        <v>2.356260119502798</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735739738707102</v>
+        <v>4.736986764613957</v>
       </c>
       <c r="K17" t="n">
-        <v>17.82416953183818</v>
+        <v>18.35506923786373</v>
       </c>
       <c r="L17" t="n">
-        <v>44.01850251385295</v>
+        <v>44.13344769848867</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92846460880703</v>
+        <v>99.92153348040533</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.90038472664378</v>
+        <v>79.1570544523733</v>
       </c>
       <c r="C18" t="n">
-        <v>36.14185383298496</v>
+        <v>35.30840895384299</v>
       </c>
       <c r="D18" t="n">
-        <v>1.286032329025279</v>
+        <v>1.257304740707944</v>
       </c>
       <c r="E18" t="n">
-        <v>12.20159945702743</v>
+        <v>11.95632803768605</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582845991777424</v>
+        <v>0.7585450916672427</v>
       </c>
       <c r="G18" t="n">
-        <v>21.92294616237597</v>
+        <v>21.36545029605317</v>
       </c>
       <c r="H18" t="n">
-        <v>37.20096286024761</v>
+        <v>37.11334444241368</v>
       </c>
       <c r="I18" t="n">
-        <v>1.791280573928857</v>
+        <v>1.965175020924952</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739278744860891</v>
+        <v>4.740906822920268</v>
       </c>
       <c r="K18" t="n">
-        <v>20.09961527335622</v>
+        <v>20.84294554762669</v>
       </c>
       <c r="L18" t="n">
-        <v>43.69886612852039</v>
+        <v>43.78319382854411</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94033523486158</v>
+        <v>99.9345483300138</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.0387636714886</v>
+        <v>78.1431250583813</v>
       </c>
       <c r="C19" t="n">
-        <v>35.55603046105248</v>
+        <v>34.59663974725085</v>
       </c>
       <c r="D19" t="n">
-        <v>1.255530597980917</v>
+        <v>1.221291149314888</v>
       </c>
       <c r="E19" t="n">
-        <v>12.16115125092682</v>
+        <v>11.88698889262674</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587622677880488</v>
+        <v>0.7590753565314978</v>
       </c>
       <c r="G19" t="n">
-        <v>21.40298426682111</v>
+        <v>20.75346930848649</v>
       </c>
       <c r="H19" t="n">
-        <v>37.22439698016878</v>
+        <v>37.13928871753852</v>
       </c>
       <c r="I19" t="n">
-        <v>1.493674134127607</v>
+        <v>1.638790655561301</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742264173675306</v>
+        <v>4.744220978321862</v>
       </c>
       <c r="K19" t="n">
-        <v>20.9612363285114</v>
+        <v>21.85687494161872</v>
       </c>
       <c r="L19" t="n">
-        <v>43.43297541671588</v>
+        <v>43.49189711610475</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95024220627977</v>
+        <v>99.9454118049743</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.64648995316519</v>
+        <v>75.49854218006641</v>
       </c>
       <c r="C20" t="n">
-        <v>33.39360940604454</v>
+        <v>32.20385164191718</v>
       </c>
       <c r="D20" t="n">
-        <v>1.16990308299598</v>
+        <v>1.126588300886999</v>
       </c>
       <c r="E20" t="n">
-        <v>11.53932465951169</v>
+        <v>11.19298063006238</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591732300794817</v>
+        <v>0.7595333183192747</v>
       </c>
       <c r="G20" t="n">
-        <v>19.9432951449655</v>
+        <v>19.14417846954363</v>
       </c>
       <c r="H20" t="n">
-        <v>37.24455853027429</v>
+        <v>37.1616954192072</v>
       </c>
       <c r="I20" t="n">
-        <v>1.245402617341477</v>
+        <v>1.366482802551463</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744832687996761</v>
+        <v>4.747083239495468</v>
       </c>
       <c r="K20" t="n">
-        <v>23.35351004683481</v>
+        <v>24.50145781993356</v>
       </c>
       <c r="L20" t="n">
-        <v>43.21138959895043</v>
+        <v>43.2491685754948</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95850905182978</v>
+        <v>99.95447803734555</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.54560574096638</v>
+        <v>81.71257317895888</v>
       </c>
       <c r="C21" t="n">
-        <v>36.99915394832606</v>
+        <v>35.92740852826722</v>
       </c>
       <c r="D21" t="n">
-        <v>1.170780630660941</v>
+        <v>1.127568442390246</v>
       </c>
       <c r="E21" t="n">
-        <v>13.4978489769797</v>
+        <v>13.23412043782122</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597426881012961</v>
+        <v>0.7601941188333559</v>
       </c>
       <c r="G21" t="n">
-        <v>21.59853482429964</v>
+        <v>20.83678268338861</v>
       </c>
       <c r="H21" t="n">
-        <v>38.91277593699914</v>
+        <v>38.86997502763415</v>
       </c>
       <c r="I21" t="n">
-        <v>1.857530883292554</v>
+        <v>2.132719226182821</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748391800633102</v>
+        <v>4.751213242708475</v>
       </c>
       <c r="K21" t="n">
-        <v>17.45439425903362</v>
+        <v>18.28742682104112</v>
       </c>
       <c r="L21" t="n">
-        <v>45.48458050636022</v>
+        <v>45.71413580552456</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93812871371991</v>
+        <v>99.92897115483291</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_63_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_63_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.49730653489574</v>
+        <v>43.62310596723992</v>
       </c>
       <c r="M2" t="n">
-        <v>98.27141251401321</v>
+        <v>96.50491354142903</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.10746329115638</v>
+        <v>81.56730947486402</v>
       </c>
       <c r="C3" t="n">
-        <v>45.96918684753438</v>
+        <v>43.32286503041958</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228905365673211</v>
+        <v>2.184598666134157</v>
       </c>
       <c r="E3" t="n">
-        <v>5.733848735172391</v>
+        <v>4.166619079994521</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429684552244036</v>
+        <v>0.737696722072001</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98634711897323</v>
+        <v>32.86000493643463</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17654894032256</v>
+        <v>33.93404921531204</v>
       </c>
       <c r="I3" t="n">
-        <v>6.595291830638066</v>
+        <v>3.073736341966671</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643552845152522</v>
+        <v>4.610604512950006</v>
       </c>
       <c r="K3" t="n">
-        <v>11.89253670884362</v>
+        <v>18.43269052513597</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90155784866645</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7632814050445</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.13225206824448</v>
+        <v>88.67744891353281</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63287120638661</v>
+        <v>42.92358474642575</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181676064127546</v>
+        <v>2.190342804711425</v>
       </c>
       <c r="E4" t="n">
-        <v>6.530294378226596</v>
+        <v>6.554510364345915</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445338974800059</v>
+        <v>0.7396364065848896</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26619476919736</v>
+        <v>33.55195755728899</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24855928408027</v>
+        <v>34.02327470290492</v>
       </c>
       <c r="I4" t="n">
-        <v>5.507656815882666</v>
+        <v>6.994999536541122</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653336859250036</v>
+        <v>4.622727541155561</v>
       </c>
       <c r="K4" t="n">
-        <v>12.86774793175553</v>
+        <v>11.32255108646718</v>
       </c>
       <c r="L4" t="n">
-        <v>44.3161783110068</v>
+        <v>45.52130899166045</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81679744914894</v>
+        <v>99.76744482455339</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.02818229230078</v>
+        <v>87.62624461148044</v>
       </c>
       <c r="C5" t="n">
-        <v>42.38358166862708</v>
+        <v>42.95677054428734</v>
       </c>
       <c r="D5" t="n">
-        <v>2.128080222382072</v>
+        <v>2.140652888398412</v>
       </c>
       <c r="E5" t="n">
-        <v>7.136183941276451</v>
+        <v>7.379502143427276</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458603176757821</v>
+        <v>0.7412801474752241</v>
       </c>
       <c r="G5" t="n">
-        <v>32.44896541987276</v>
+        <v>32.790800920267</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30957461308597</v>
+        <v>34.0988867838603</v>
       </c>
       <c r="I5" t="n">
-        <v>4.597890792534119</v>
+        <v>5.842120806332073</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661626985473638</v>
+        <v>4.633000921720151</v>
       </c>
       <c r="K5" t="n">
-        <v>13.97181770769922</v>
+        <v>12.37375538851955</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49161015656586</v>
+        <v>44.47516852451142</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84700953289214</v>
+        <v>99.80569445731831</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.81466970465333</v>
+        <v>86.3575119779328</v>
       </c>
       <c r="C6" t="n">
-        <v>41.88417325696712</v>
+        <v>42.59490913356642</v>
       </c>
       <c r="D6" t="n">
-        <v>2.069286615851562</v>
+        <v>2.080372848472045</v>
       </c>
       <c r="E6" t="n">
-        <v>7.578587815132032</v>
+        <v>7.984631246649313</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469851742689512</v>
+        <v>0.7426757674115206</v>
       </c>
       <c r="G6" t="n">
-        <v>31.55248055752925</v>
+        <v>31.86742338465443</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36131801637175</v>
+        <v>34.16308530092994</v>
       </c>
       <c r="I6" t="n">
-        <v>3.837354186318828</v>
+        <v>4.877599883493553</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668657339180944</v>
+        <v>4.641723546322004</v>
       </c>
       <c r="K6" t="n">
-        <v>15.18533029534668</v>
+        <v>13.64248802206718</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80277725900471</v>
+        <v>43.60032171085718</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87228081131852</v>
+        <v>99.83771886649079</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.3796056150528</v>
+        <v>84.86209785574704</v>
       </c>
       <c r="C7" t="n">
-        <v>41.0452419323922</v>
+        <v>41.85713355326453</v>
       </c>
       <c r="D7" t="n">
-        <v>1.999767082861641</v>
+        <v>2.009389750733537</v>
       </c>
       <c r="E7" t="n">
-        <v>7.857626464491908</v>
+        <v>8.390720399754425</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479413486249437</v>
+        <v>0.7438634027170159</v>
       </c>
       <c r="G7" t="n">
-        <v>30.49244677766047</v>
+        <v>30.78009500962361</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4053020367474</v>
+        <v>34.21771652498273</v>
       </c>
       <c r="I7" t="n">
-        <v>3.201888475760537</v>
+        <v>4.07116650095437</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674633428905897</v>
+        <v>4.64914626698135</v>
       </c>
       <c r="K7" t="n">
-        <v>16.62039438494722</v>
+        <v>15.13790214425295</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22777051081838</v>
+        <v>42.86947541682991</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89340682815779</v>
+        <v>99.86451111434741</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.18537967157906</v>
+        <v>83.11993638304583</v>
       </c>
       <c r="C8" t="n">
-        <v>43.36058359999819</v>
+        <v>40.7473468819266</v>
       </c>
       <c r="D8" t="n">
-        <v>2.003978364054869</v>
+        <v>1.927002675589396</v>
       </c>
       <c r="E8" t="n">
-        <v>9.695399052763799</v>
+        <v>8.612902256711942</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495164277239531</v>
+        <v>0.7448768370915085</v>
       </c>
       <c r="G8" t="n">
-        <v>31.00300219469264</v>
+        <v>29.51807901716824</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47775567530184</v>
+        <v>34.26433450620939</v>
       </c>
       <c r="I8" t="n">
-        <v>5.57125028376726</v>
+        <v>3.397260858453426</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684477673274706</v>
+        <v>4.655480231821929</v>
       </c>
       <c r="K8" t="n">
-        <v>11.81462032842093</v>
+        <v>16.88006361695417</v>
       </c>
       <c r="L8" t="n">
-        <v>44.63947798751872</v>
+        <v>42.25950154275938</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81468191593784</v>
+        <v>99.88691204164016</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.11800316046502</v>
+        <v>81.22900478965208</v>
       </c>
       <c r="C9" t="n">
-        <v>42.15830428975556</v>
+        <v>39.38377097906366</v>
       </c>
       <c r="D9" t="n">
-        <v>1.91039156764274</v>
+        <v>1.838174292417126</v>
       </c>
       <c r="E9" t="n">
-        <v>10.01779682819172</v>
+        <v>8.688266836500217</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508657587833297</v>
+        <v>0.745743209414206</v>
       </c>
       <c r="G9" t="n">
-        <v>29.55514641610597</v>
+        <v>28.15739422587993</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53982490403316</v>
+        <v>34.30418763305347</v>
       </c>
       <c r="I9" t="n">
-        <v>4.65106669331229</v>
+        <v>2.83434353354835</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69291099239581</v>
+        <v>4.660895058838788</v>
       </c>
       <c r="K9" t="n">
-        <v>13.88199683953498</v>
+        <v>18.77099521034791</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80494191838259</v>
+        <v>41.75086545340917</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84524304767312</v>
+        <v>99.90563164282074</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.73406940176716</v>
+        <v>86.0546567427787</v>
       </c>
       <c r="C10" t="n">
-        <v>40.49624829720818</v>
+        <v>42.7242890324645</v>
       </c>
       <c r="D10" t="n">
-        <v>1.803389104520092</v>
+        <v>1.840213621145401</v>
       </c>
       <c r="E10" t="n">
-        <v>10.103672255109</v>
+        <v>10.58576813520486</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520260867881906</v>
+        <v>0.7465705605294667</v>
       </c>
       <c r="G10" t="n">
-        <v>27.89974052024764</v>
+        <v>29.59913639382991</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59319999225676</v>
+        <v>35.7527492481221</v>
       </c>
       <c r="I10" t="n">
-        <v>3.881878400419283</v>
+        <v>2.864152780637802</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700163042426191</v>
+        <v>4.666066003309167</v>
       </c>
       <c r="K10" t="n">
-        <v>16.26593059823283</v>
+        <v>13.94534325722129</v>
       </c>
       <c r="L10" t="n">
-        <v>43.10862480752255</v>
+        <v>43.23500175297051</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87080370296356</v>
+        <v>99.9046340426563</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.23080923475851</v>
+        <v>85.72795074175946</v>
       </c>
       <c r="C11" t="n">
-        <v>38.59471757749228</v>
+        <v>42.73252925815271</v>
       </c>
       <c r="D11" t="n">
-        <v>1.692228905149244</v>
+        <v>1.817020598393366</v>
       </c>
       <c r="E11" t="n">
-        <v>10.020752271621</v>
+        <v>10.92045847319436</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530256918352967</v>
+        <v>0.7472776115538514</v>
       </c>
       <c r="G11" t="n">
-        <v>26.18001142193362</v>
+        <v>29.28824306793426</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63918182442364</v>
+        <v>35.84876706045479</v>
       </c>
       <c r="I11" t="n">
-        <v>3.239198545825109</v>
+        <v>2.435698858017249</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706410573970604</v>
+        <v>4.670485072211572</v>
       </c>
       <c r="K11" t="n">
-        <v>18.76919076524149</v>
+        <v>14.27204925824054</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52826170169902</v>
+        <v>42.91430834111031</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89217004443279</v>
+        <v>99.91888685750357</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.7562872785368</v>
+        <v>83.85711268159264</v>
       </c>
       <c r="C12" t="n">
-        <v>36.62138502123759</v>
+        <v>41.24045319896699</v>
       </c>
       <c r="D12" t="n">
-        <v>1.583530622995482</v>
+        <v>1.737535093593312</v>
       </c>
       <c r="E12" t="n">
-        <v>9.827484603962036</v>
+        <v>10.78130805721934</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538869950836452</v>
+        <v>0.7478810232170997</v>
       </c>
       <c r="G12" t="n">
-        <v>24.49836997279463</v>
+        <v>28.0070298626355</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67880177384768</v>
+        <v>35.87771421988109</v>
       </c>
       <c r="I12" t="n">
-        <v>2.70241959058054</v>
+        <v>2.031388029939426</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711793719272783</v>
+        <v>4.674256395106874</v>
       </c>
       <c r="K12" t="n">
-        <v>21.24371272146321</v>
+        <v>16.14288731840735</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04492451991517</v>
+        <v>42.54900118101407</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91002226261597</v>
+        <v>99.93234169838841</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.28235821191839</v>
+        <v>85.02351731153126</v>
       </c>
       <c r="C13" t="n">
-        <v>34.56467918246471</v>
+        <v>42.22405702412519</v>
       </c>
       <c r="D13" t="n">
-        <v>1.47588777608043</v>
+        <v>1.738806879521835</v>
       </c>
       <c r="E13" t="n">
-        <v>9.535152511467023</v>
+        <v>11.42028075386317</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546296037405491</v>
+        <v>0.7484284334910237</v>
       </c>
       <c r="G13" t="n">
-        <v>22.83305687410544</v>
+        <v>28.34744678572216</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71296177206526</v>
+        <v>36.22389207732257</v>
       </c>
       <c r="I13" t="n">
-        <v>2.254234651081253</v>
+        <v>1.86698467229159</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716435023378432</v>
+        <v>4.677677709318899</v>
       </c>
       <c r="K13" t="n">
-        <v>23.71764178808159</v>
+        <v>14.97648268846875</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64261181860425</v>
+        <v>42.73727298289066</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92493278915056</v>
+        <v>99.9378126954846</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.47248356602283</v>
+        <v>83.09111385283111</v>
       </c>
       <c r="C14" t="n">
-        <v>38.80627723503814</v>
+        <v>40.58186282060524</v>
       </c>
       <c r="D14" t="n">
-        <v>1.477834043986564</v>
+        <v>1.658889312098947</v>
       </c>
       <c r="E14" t="n">
-        <v>11.92946610429226</v>
+        <v>11.15485686340864</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556247413130541</v>
+        <v>0.7488958511279762</v>
       </c>
       <c r="G14" t="n">
-        <v>24.69452656964077</v>
+        <v>27.04456547299831</v>
       </c>
       <c r="H14" t="n">
-        <v>36.59009761648097</v>
+        <v>36.24651506340692</v>
       </c>
       <c r="I14" t="n">
-        <v>3.30227985710262</v>
+        <v>1.556792220240459</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722654633206589</v>
+        <v>4.680599069549852</v>
       </c>
       <c r="K14" t="n">
-        <v>16.52751643397716</v>
+        <v>16.90888614716888</v>
       </c>
       <c r="L14" t="n">
-        <v>44.5562753028893</v>
+        <v>42.45739034688446</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89006897190461</v>
+        <v>99.94813931465858</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.58961749054775</v>
+        <v>82.23630612674344</v>
       </c>
       <c r="C15" t="n">
-        <v>38.43323536391071</v>
+        <v>39.94611080392634</v>
       </c>
       <c r="D15" t="n">
-        <v>1.445195954943731</v>
+        <v>1.622710116482328</v>
       </c>
       <c r="E15" t="n">
-        <v>12.12516279932763</v>
+        <v>11.135701263768</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564649259120343</v>
+        <v>0.7492950312234737</v>
       </c>
       <c r="G15" t="n">
-        <v>24.14914587528598</v>
+        <v>26.45969666200037</v>
       </c>
       <c r="H15" t="n">
-        <v>36.63078240988666</v>
+        <v>36.27078927658349</v>
       </c>
       <c r="I15" t="n">
-        <v>2.754959738241501</v>
+        <v>1.315019831539071</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727905786950215</v>
+        <v>4.683093945146712</v>
       </c>
       <c r="K15" t="n">
-        <v>17.41038250945223</v>
+        <v>17.76369387325657</v>
       </c>
       <c r="L15" t="n">
-        <v>44.06465213060641</v>
+        <v>42.24638468059324</v>
       </c>
       <c r="M15" t="n">
-        <v>99.90827000396936</v>
+        <v>99.95618935777615</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.97468339290117</v>
+        <v>79.85950475223895</v>
       </c>
       <c r="C16" t="n">
-        <v>36.24366875480077</v>
+        <v>37.77324334223899</v>
       </c>
       <c r="D16" t="n">
-        <v>1.346294868212239</v>
+        <v>1.525063844506811</v>
       </c>
       <c r="E16" t="n">
-        <v>11.67838460522143</v>
+        <v>10.64833778579193</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571894699578133</v>
+        <v>0.7496379211579958</v>
       </c>
       <c r="G16" t="n">
-        <v>22.49651409027928</v>
+        <v>24.86748945850537</v>
       </c>
       <c r="H16" t="n">
-        <v>36.66586746720814</v>
+        <v>36.28738739620508</v>
       </c>
       <c r="I16" t="n">
-        <v>2.29799870478592</v>
+        <v>1.096351338834293</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732434187236334</v>
+        <v>4.685237007237474</v>
       </c>
       <c r="K16" t="n">
-        <v>20.02531660709882</v>
+        <v>20.14049524776106</v>
       </c>
       <c r="L16" t="n">
-        <v>43.6544879787048</v>
+        <v>42.04973308134608</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9234733406044</v>
+        <v>99.96347167134614</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.64493076213625</v>
+        <v>84.60413432723108</v>
       </c>
       <c r="C17" t="n">
-        <v>37.43301654405293</v>
+        <v>40.89864410823706</v>
       </c>
       <c r="D17" t="n">
-        <v>1.347589996959547</v>
+        <v>1.525809790050327</v>
       </c>
       <c r="E17" t="n">
-        <v>12.46384629212229</v>
+        <v>12.31181863247365</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757917882338233</v>
+        <v>0.7500045871625389</v>
       </c>
       <c r="G17" t="n">
-        <v>22.89967274225495</v>
+        <v>26.33101561273419</v>
       </c>
       <c r="H17" t="n">
-        <v>37.08265696434449</v>
+        <v>37.75649929820749</v>
       </c>
       <c r="I17" t="n">
-        <v>2.356260119502798</v>
+        <v>1.241457736837026</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736986764613957</v>
+        <v>4.687528669765868</v>
       </c>
       <c r="K17" t="n">
-        <v>18.35506923786373</v>
+        <v>15.3958656727689</v>
       </c>
       <c r="L17" t="n">
-        <v>44.13344769848867</v>
+        <v>43.66412852543564</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92153348040533</v>
+        <v>99.95863830644161</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.1570544523733</v>
+        <v>86.20361732194411</v>
       </c>
       <c r="C18" t="n">
-        <v>35.30840895384299</v>
+        <v>41.64049893418182</v>
       </c>
       <c r="D18" t="n">
-        <v>1.257304740707944</v>
+        <v>1.527020687109879</v>
       </c>
       <c r="E18" t="n">
-        <v>11.95632803768605</v>
+        <v>12.91722486873617</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7585450916672427</v>
+        <v>0.750599797886161</v>
       </c>
       <c r="G18" t="n">
-        <v>21.36545029605317</v>
+        <v>26.47869987366813</v>
       </c>
       <c r="H18" t="n">
-        <v>37.11334444241368</v>
+        <v>37.78646321263333</v>
       </c>
       <c r="I18" t="n">
-        <v>1.965175020924952</v>
+        <v>2.052360145121922</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740906822920268</v>
+        <v>4.691248736788507</v>
       </c>
       <c r="K18" t="n">
-        <v>20.84294554762669</v>
+        <v>13.79638267805592</v>
       </c>
       <c r="L18" t="n">
-        <v>43.78319382854411</v>
+        <v>44.49476063228519</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9345483300138</v>
+        <v>99.93164224452293</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.1431250583813</v>
+        <v>83.52424130499074</v>
       </c>
       <c r="C19" t="n">
-        <v>34.59663974725085</v>
+        <v>39.27921923060281</v>
       </c>
       <c r="D19" t="n">
-        <v>1.221291149314888</v>
+        <v>1.428015717694026</v>
       </c>
       <c r="E19" t="n">
-        <v>11.88698889262674</v>
+        <v>12.36497637705864</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7590753565314978</v>
+        <v>0.7511124744999208</v>
       </c>
       <c r="G19" t="n">
-        <v>20.75346930848649</v>
+        <v>24.76194325518008</v>
       </c>
       <c r="H19" t="n">
-        <v>37.13928871753852</v>
+        <v>37.81227222039001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.638790655561301</v>
+        <v>1.711468294543538</v>
       </c>
       <c r="J19" t="n">
-        <v>4.744220978321862</v>
+        <v>4.694452965624505</v>
       </c>
       <c r="K19" t="n">
-        <v>21.85687494161872</v>
+        <v>16.47575869500927</v>
       </c>
       <c r="L19" t="n">
-        <v>43.49189711610475</v>
+        <v>44.18801207035677</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9454118049743</v>
+        <v>99.94298999596884</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.49854218006641</v>
+        <v>80.74593457188041</v>
       </c>
       <c r="C20" t="n">
-        <v>32.20385164191718</v>
+        <v>36.76544502112009</v>
       </c>
       <c r="D20" t="n">
-        <v>1.126588300886999</v>
+        <v>1.3258921397643</v>
       </c>
       <c r="E20" t="n">
-        <v>11.19298063006238</v>
+        <v>11.71854742214837</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7595333183192747</v>
+        <v>0.7515549675373467</v>
       </c>
       <c r="G20" t="n">
-        <v>19.14417846954363</v>
+        <v>22.99110963592878</v>
       </c>
       <c r="H20" t="n">
-        <v>37.1616954192072</v>
+        <v>37.83454806822215</v>
       </c>
       <c r="I20" t="n">
-        <v>1.366482802551463</v>
+        <v>1.427063791171046</v>
       </c>
       <c r="J20" t="n">
-        <v>4.747083239495468</v>
+        <v>4.697218547108418</v>
       </c>
       <c r="K20" t="n">
-        <v>24.50145781993356</v>
+        <v>19.25406542811957</v>
       </c>
       <c r="L20" t="n">
-        <v>43.2491685754948</v>
+        <v>43.93294876480081</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95447803734555</v>
+        <v>99.95245921404047</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.71257317895888</v>
+        <v>77.86508429106155</v>
       </c>
       <c r="C21" t="n">
-        <v>35.92740852826722</v>
+        <v>34.10445718888923</v>
       </c>
       <c r="D21" t="n">
-        <v>1.127568442390246</v>
+        <v>1.220515480455294</v>
       </c>
       <c r="E21" t="n">
-        <v>13.23412043782122</v>
+        <v>10.98550791561232</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7601941188333559</v>
+        <v>0.7519377746785663</v>
       </c>
       <c r="G21" t="n">
-        <v>20.83678268338861</v>
+        <v>21.16386724223608</v>
       </c>
       <c r="H21" t="n">
-        <v>38.86997502763415</v>
+        <v>37.85381922710064</v>
       </c>
       <c r="I21" t="n">
-        <v>2.132719226182821</v>
+        <v>1.189825559237612</v>
       </c>
       <c r="J21" t="n">
-        <v>4.751213242708475</v>
+        <v>4.69961109174104</v>
       </c>
       <c r="K21" t="n">
-        <v>18.28742682104112</v>
+        <v>22.13491570893846</v>
       </c>
       <c r="L21" t="n">
-        <v>45.71413580552456</v>
+        <v>43.72098644130644</v>
       </c>
       <c r="M21" t="n">
-        <v>99.92897115483291</v>
+        <v>99.96035933913413</v>
       </c>
     </row>
   </sheetData>
